--- a/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PCAR_YR_FIN.xlsx
@@ -2923,10 +2923,10 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2349700</v>
+        <v>1455200</v>
       </c>
       <c r="E57" s="3">
-        <v>2699500</v>
+        <v>1598700</v>
       </c>
       <c r="F57" s="3">
         <v>1667600</v>
@@ -2974,7 +2974,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8387400</v>
+        <v>8379900</v>
       </c>
       <c r="E58" s="3">
         <v>5544700</v>
